--- a/request_forms/004_video_to_text_conversion_request--request_forms.xlsx
+++ b/request_forms/004_video_to_text_conversion_request--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -730,12 +730,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'en'}</t>
+          <t>en</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'en'}</t>
+          <t>en</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'es'}</t>
+          <t>es</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'es'}</t>
+          <t>es</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'fr'}</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'fr'}</t>
+          <t>fr</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'zh'}</t>
+          <t>zh</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'zh'}</t>
+          <t>zh</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'mp3'}</t>
+          <t>mp3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'mp3'}</t>
+          <t>mp3</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'wav'}</t>
+          <t>wav</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'wav'}</t>
+          <t>wav</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'4k'}</t>
+          <t>4k</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': '4K'}</t>
+          <t>4K</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'8k'}</t>
+          <t>8k</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': '8K'}</t>
+          <t>8K</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'1080p'}</t>
+          <t>1080p</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': '1080p'}</t>
+          <t>1080p</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'1080i'}</t>
+          <t>1080i</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': '1080i'}</t>
+          <t>1080i</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'2k'}</t>
+          <t>2k</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': '2K'}</t>
+          <t>2K</t>
         </is>
       </c>
     </row>
@@ -950,29 +950,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'4k'}</t>
+          <t>6k</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': '4K'}</t>
+          <t>6K</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>file_format_choices</t>
+          <t>transcription_speed_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'6k'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': '6K'}</t>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'normal'}</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'normal'}</t>
+          <t>fast</t>
         </is>
       </c>
     </row>
@@ -1001,29 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'fast'}</t>
+          <t>priority</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'fast'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>transcription_speed_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'value':_'priority'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'value': 'priority'}</t>
+          <t>priority</t>
         </is>
       </c>
     </row>
